--- a/data/Test Data.xlsx
+++ b/data/Test Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamed.abbas\Desktop\AutomationFramework\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Automation\AutomationFramework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D57B98-E8BD-4712-984B-B629F94E364A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41F9770-833D-47A6-9341-B99F66DEFEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{989DF447-24D7-4921-BF4F-FB4FE5A17306}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{989DF447-24D7-4921-BF4F-FB4FE5A17306}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>testCases</t>
-  </si>
-  <si>
-    <t>valid</t>
   </si>
   <si>
     <t>userId</t>
@@ -56,10 +53,7 @@
     <t>title</t>
   </si>
   <si>
-    <t xml:space="preserve">This is test </t>
-  </si>
-  <si>
-    <t>Test</t>
+    <t>valid</t>
   </si>
 </sst>
 </file>
@@ -491,16 +485,16 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
@@ -508,20 +502,12 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4">
-        <v>10</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" s="4"/>
     </row>
